--- a/Laska_etal_2009/Laska_etal_2009_registry_rows.xlsx
+++ b/Laska_etal_2009/Laska_etal_2009_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R794346c251f7406d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="Rc23d6b5d4f304e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="R52cddadcb70a472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rb2b2f382815f4932"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R843c332f307744d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rdcca8e45606e4ef4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Avoidance thresholds for six bitter compounds</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Source tables / results to select</x:v>
+        <x:v>Table 1: Comparative taste-avoidance thresholds for six bitter tastants</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — optional taste extension; gap required
@@ -350,13 +350,13 @@
         <x:v>Source citation and endpoint in existing source notes; Nick/Fran dissertation reference check.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF pp. 8–9 / printed pp. 567–568, including continuation. Combines this study and cited earlier studies across taxa; retain source, species, compound and sucrose background. Figures 1–3 describe the present-study response curves; avoid double-counting.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/0304089121/Laska-2009-Gustatory responsiveness to six bit.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +508,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Laska, M., Rivas Bautista, R. M., &amp; Hernandez Salazar, L. T. (2009). Gustatory responsiveness to six bitter tastants in three species of nonhuman primates. Journal of Chemical Ecology, 35, 560–571. https://doi.org/10.1007/s10886-009-9630-8</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Table 1</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant addition; not found in dissertation references. Planned folder: Laska_etal_2009. Target: Source tables / results to select. Squirrel monkeys, spider monkeys and pigtail macaques. Preserve solvent/background sucrose, compound, threshold criterion and individual sample sizes.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF pp. 8–9 / printed pp. 567–568, including continuation. Combines this study and cited earlier studies across taxa; retain source, species, compound and sucrose background. Figures 1–3 describe the present-study response curves; avoid double-counting. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/0304089121/Laska-2009-Gustatory responsiveness to six bit.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — optional taste extension; gap required</x:v>
@@ -550,7 +552,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Avoidance thresholds for six bitter compounds</x:v>
+        <x:v>Comparative taste-avoidance thresholds for six bitter tastants</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -563,7 +565,7 @@
       <x:c r="AC2" s="3"/>
       <x:c r="AD2" s="3"/>
       <x:c r="AE2" s="3" t="str">
-        <x:v>primary</x:v>
+        <x:v>both</x:v>
       </x:c>
       <x:c r="AF2" s="3"/>
       <x:c r="AG2" s="3" t="str">
@@ -695,7 +697,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="100" customHeight="1">
@@ -703,7 +705,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -987,13 +989,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D9252A2-D29F-47A2-92FB-C9194E9F835F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AD20595-B3E3-4A6A-951D-5B8108929913}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1A60B60-0D66-42ED-8D22-2AB514C9E6C6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00FBD5F9-78EC-4ECF-9DCF-9646B3007F26}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5D35939-9D3B-461C-9AD6-CD15B1008E81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84762B46-E1C9-4D5A-BCB6-5239BE93EBD6}"/>
 </file>